--- a/artfynd/A 419-2025 artfynd.xlsx
+++ b/artfynd/A 419-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93426486</v>
+        <v>53188699</v>
       </c>
       <c r="B2" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>1286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Luddfingerört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Potentilla heptaphylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnnäs, 500 m SSV, Sk</t>
+          <t>Brudasten, 1,1 km NNO, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450974.3726677638</v>
+        <v>451182</v>
       </c>
       <c r="R2" t="n">
-        <v>6207005.472761672</v>
+        <v>6206815</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-05-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>talrik</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,83 +759,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>mindre damm</t>
+          <t>betad torrbacke</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Åke Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Faunaväkteri groddjur</t>
-        </is>
-      </c>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93426280</v>
+        <v>93426073</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>100031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vit stork</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Ciconia ciconia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnnäs, 400 m SV, Sk</t>
+          <t>Kvarnäsviken, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450965.3386784039</v>
+        <v>450891</v>
       </c>
       <c r="R3" t="n">
-        <v>6207196.207578214</v>
+        <v>6207025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,40 +850,19 @@
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hörd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>mindre damm</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -931,23 +875,14 @@
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Faunaväkteri groddjur</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113253129</v>
+        <v>93426074</v>
       </c>
       <c r="B4" t="n">
-        <v>109545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,38 +890,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>102992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnnäs, Sk</t>
+          <t>Kvarnäsviken, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451064</v>
+        <v>450891</v>
       </c>
       <c r="R4" t="n">
-        <v>6206861</v>
+        <v>6207025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,24 +962,785 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93426072</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnäsviken, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>450891</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6207025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>93426280</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarnnäs, 400 m SV, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6207196</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>mindre damm</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Faunaväkteri groddjur</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>93426486</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvarnnäs, 500 m SSV, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450974</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6207005</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>mindre damm</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Faunaväkteri groddjur</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113253129</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnnäs, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>451064</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6206861</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Johan Ennerfelt</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Johan Ennerfelt, Robert Ennerfelt</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>NVI och fördjupad artinventering av vedinsekter och svampar i Ekenabben och Kvarnnäs naturreservat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>53188690</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brudasten, 1,1 km NNO, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>451182</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6206815</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-05-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-05-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>betad torrbacke</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>53188706</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brudasten, 1,1 km NNO, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>451182</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6206815</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-05-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-05-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>betad torrbacke</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110657554</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99706</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222738</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plattsäv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Blysmus compressus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Panz. ex Link</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarnnäs, 700 m SSV, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>451190</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6206743</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>M-Kri-1098</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fin lokal</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 419-2025 artfynd.xlsx
+++ b/artfynd/A 419-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53188699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93426073</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93426074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93426072</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t>Faunaväkteri groddjur</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93426280</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Faunaväkteri groddjur</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93426486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t>NVI och fördjupad artinventering av vedinsekter och svampar i Ekenabben och Kvarnnäs naturreservat</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113253129</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53188690</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53188706</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,8 +1793,25 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110657554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>